--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_gj_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_gj_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -812,7 +812,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="n">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="n">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="n">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="n">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>06-05-2021 08:30</t>
+          <t>2021-06-05 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>04-06-2021 08:30</t>
+          <t>2021-04-06 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="n">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>04-09-2021 08:30</t>
+          <t>2021-04-09 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="n">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="n">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="n">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>02-12-2021 08:30</t>
+          <t>2021-02-12 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="n">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -3355,7 +3355,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>01-06-2021 08:30</t>
+          <t>2021-01-06 08:30:00</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>01-07-2021 08:30</t>
+          <t>2021-01-07 08:30:00</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T38" t="inlineStr"/>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T43" t="inlineStr"/>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T44" t="inlineStr"/>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T46" t="inlineStr"/>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T47" t="n">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T48" t="n">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T49" t="n">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T50" t="n">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T51" t="n">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>01-06-2021 08:30</t>
+          <t>2021-01-06 08:30:00</t>
         </is>
       </c>
       <c r="T52" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T53" t="n">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>04-08-2021 08:30</t>
+          <t>2021-04-08 08:30:00</t>
         </is>
       </c>
       <c r="T54" t="n">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T55" t="n">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T56" t="n">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T57" t="n">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>02-12-2021 08:30</t>
+          <t>2021-02-12 08:30:00</t>
         </is>
       </c>
       <c r="T58" t="n">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T59" t="inlineStr"/>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T60" t="inlineStr"/>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T61" t="inlineStr"/>
@@ -6302,7 +6302,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T62" t="n">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T63" t="n">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T64" t="inlineStr"/>
@@ -6593,7 +6593,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T65" t="inlineStr"/>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T66" t="inlineStr"/>
@@ -6779,7 +6779,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T67" t="inlineStr"/>
@@ -6872,7 +6872,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T68" t="inlineStr"/>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T69" t="inlineStr"/>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T70" t="inlineStr"/>
@@ -7151,7 +7151,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T71" t="inlineStr"/>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T72" t="inlineStr"/>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T73" t="inlineStr"/>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T74" t="inlineStr"/>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T75" t="inlineStr"/>
@@ -7616,7 +7616,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T76" t="inlineStr"/>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T77" t="inlineStr"/>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T78" t="inlineStr"/>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T79" t="inlineStr"/>
@@ -7988,7 +7988,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T80" t="inlineStr"/>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T81" t="inlineStr"/>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T82" t="inlineStr"/>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T83" t="inlineStr"/>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T84" t="inlineStr"/>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T85" t="n">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T86" t="n">
@@ -8643,7 +8643,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T87" t="n">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T88" t="n">
@@ -8833,7 +8833,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T89" t="n">
@@ -8928,7 +8928,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>01-06-2021 08:30</t>
+          <t>2021-01-06 08:30:00</t>
         </is>
       </c>
       <c r="T90" t="n">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>01-07-2021 08:30</t>
+          <t>2021-01-07 08:30:00</t>
         </is>
       </c>
       <c r="T91" t="n">
@@ -9118,7 +9118,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T92" t="n">
@@ -9213,7 +9213,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T93" t="n">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T94" t="n">
@@ -9403,7 +9403,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T95" t="n">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T96" t="n">
@@ -9593,7 +9593,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T97" t="n">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T98" t="n">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T99" t="n">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T100" t="n">
@@ -9995,7 +9995,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T101" t="n">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T102" t="n">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T103" t="n">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T104" t="n">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T105" t="n">
@@ -10498,7 +10498,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T106" t="n">
@@ -10597,7 +10597,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T107" t="n">
@@ -10698,7 +10698,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T108" t="n">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T109" t="n">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T110" t="n">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T111" t="n">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T112" t="n">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T113" t="n">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T114" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T115" t="n">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T116" t="n">
@@ -11589,7 +11589,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T117" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T118" t="n">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T119" t="n">
@@ -11888,7 +11888,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T120" t="n">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T121" t="n">
@@ -12086,7 +12086,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T122" t="n">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T123" t="n">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T124" t="n">
@@ -12385,7 +12385,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T125" t="n">
@@ -12484,7 +12484,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>02-04-2021 08:30</t>
+          <t>2021-02-04 08:30:00</t>
         </is>
       </c>
       <c r="T126" t="n">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T127" t="n">
@@ -12686,7 +12686,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T128" t="n">
@@ -12787,7 +12787,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T129" t="n">
@@ -12886,7 +12886,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T130" t="n">
@@ -12985,7 +12985,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T131" t="n">
@@ -13084,7 +13084,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>04-04-2021 08:30</t>
+          <t>2021-04-04 08:30:00</t>
         </is>
       </c>
       <c r="T132" t="n">
@@ -13183,7 +13183,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>02-10-2021 08:30</t>
+          <t>2021-02-10 08:30:00</t>
         </is>
       </c>
       <c r="T133" t="n">
@@ -13282,7 +13282,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T134" t="n">
@@ -13381,7 +13381,7 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T135" t="n">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T136" t="n">
@@ -13581,7 +13581,7 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T137" t="n">
@@ -13682,7 +13682,7 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T138" t="n">
@@ -13781,7 +13781,7 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T139" t="n">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T140" t="n">
@@ -13981,7 +13981,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T141" t="n">
@@ -14080,7 +14080,7 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T142" t="n">
@@ -14181,7 +14181,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T143" t="n">
@@ -14280,7 +14280,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T144" t="n">
@@ -14381,7 +14381,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T145" t="n">
@@ -14480,7 +14480,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T146" t="n">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T147" t="n">
@@ -14678,7 +14678,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T148" t="n">
@@ -14779,7 +14779,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>02-10-2021 08:30</t>
+          <t>2021-02-10 08:30:00</t>
         </is>
       </c>
       <c r="T149" t="n">
@@ -14878,7 +14878,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T150" t="n">
@@ -14977,7 +14977,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T151" t="n">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T152" t="n">
@@ -15175,7 +15175,7 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T153" t="n">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T154" t="n">
@@ -15373,7 +15373,7 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T155" t="n">
@@ -15474,7 +15474,7 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>04-04-2021 08:30</t>
+          <t>2021-04-04 08:30:00</t>
         </is>
       </c>
       <c r="T156" t="n">
@@ -15573,7 +15573,7 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>02-10-2021 08:30</t>
+          <t>2021-02-10 08:30:00</t>
         </is>
       </c>
       <c r="T157" t="n">
@@ -15672,7 +15672,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T158" t="n">
@@ -15771,7 +15771,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T159" t="n">
@@ -15870,7 +15870,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T160" t="n">
@@ -15971,7 +15971,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T161" t="n">
@@ -16072,7 +16072,7 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T162" t="n">
@@ -16171,7 +16171,7 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T163" t="n">
@@ -16270,7 +16270,7 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T164" t="n">
@@ -16369,7 +16369,7 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T165" t="n">
@@ -16468,7 +16468,7 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T166" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T167" t="n">
@@ -16670,7 +16670,7 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T168" t="n">
@@ -16771,7 +16771,7 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T169" t="n">
@@ -16870,7 +16870,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T170" t="n">
@@ -16969,7 +16969,7 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T171" t="n">
@@ -17068,7 +17068,7 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T172" t="n">
@@ -17167,7 +17167,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T173" t="n">
@@ -17266,7 +17266,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T174" t="n">
@@ -17365,7 +17365,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T175" t="n">
@@ -17464,7 +17464,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T176" t="n">
@@ -17565,7 +17565,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T177" t="n">
@@ -17664,7 +17664,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T178" t="n">
@@ -17763,7 +17763,7 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>10-12-2021 08:30</t>
+          <t>2021-10-12 08:30:00</t>
         </is>
       </c>
       <c r="T179" t="n">
@@ -17862,7 +17862,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T180" t="n">
@@ -17961,7 +17961,7 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T181" t="n">
@@ -18062,7 +18062,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T182" t="n">
@@ -18157,7 +18157,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T183" t="n">
@@ -18252,7 +18252,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T184" t="n">
@@ -18347,7 +18347,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T185" t="n">
@@ -18442,7 +18442,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T186" t="n">
@@ -18537,7 +18537,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>07-06-2021 08:30</t>
+          <t>2021-07-06 08:30:00</t>
         </is>
       </c>
       <c r="T187" t="n">
@@ -18632,7 +18632,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T188" t="n">
@@ -18727,7 +18727,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T189" t="n">
@@ -18822,7 +18822,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T190" t="n">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T191" t="n">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T192" t="n">
@@ -19107,7 +19107,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T193" t="n">
@@ -19202,7 +19202,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T194" t="n">
@@ -19297,7 +19297,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T195" t="n">
@@ -19392,7 +19392,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T196" t="n">
@@ -19487,7 +19487,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T197" t="n">
@@ -19582,7 +19582,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>03-06-2021 08:30</t>
+          <t>2021-03-06 08:30:00</t>
         </is>
       </c>
       <c r="T198" t="n">
@@ -19677,7 +19677,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>01-07-2021 08:30</t>
+          <t>2021-01-07 08:30:00</t>
         </is>
       </c>
       <c r="T199" t="n">
@@ -19772,7 +19772,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T200" t="n">
@@ -19867,7 +19867,7 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T201" t="n">
@@ -19962,7 +19962,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T202" t="n">
@@ -20057,7 +20057,7 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T203" t="n">
@@ -20152,7 +20152,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T204" t="n">
@@ -20247,7 +20247,7 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T205" t="inlineStr"/>
@@ -20340,7 +20340,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T206" t="inlineStr"/>
@@ -20433,7 +20433,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T207" t="inlineStr"/>
@@ -20526,7 +20526,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T208" t="inlineStr"/>
@@ -20619,7 +20619,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T209" t="inlineStr"/>
@@ -20712,7 +20712,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T210" t="inlineStr"/>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T211" t="inlineStr"/>
@@ -20898,7 +20898,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>04-04-2021 08:30</t>
+          <t>2021-04-04 08:30:00</t>
         </is>
       </c>
       <c r="T212" t="n">
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T213" t="n">
@@ -21096,7 +21096,7 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T214" t="inlineStr"/>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T215" t="inlineStr"/>
@@ -21282,7 +21282,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T216" t="inlineStr"/>
@@ -21375,7 +21375,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T217" t="inlineStr"/>
@@ -21468,7 +21468,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T218" t="inlineStr"/>
@@ -21561,7 +21561,7 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T219" t="inlineStr"/>
@@ -21654,7 +21654,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T220" t="inlineStr"/>
@@ -21747,7 +21747,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T221" t="inlineStr"/>
@@ -21840,7 +21840,7 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T222" t="inlineStr"/>
@@ -21933,7 +21933,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T223" t="inlineStr"/>
@@ -22026,7 +22026,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T224" t="inlineStr"/>
@@ -22119,7 +22119,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T225" t="inlineStr"/>
@@ -22212,7 +22212,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T226" t="n">
@@ -22313,7 +22313,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T227" t="n">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T228" t="n">
@@ -22509,7 +22509,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T229" t="n">
@@ -22604,7 +22604,7 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T230" t="n">
@@ -22699,7 +22699,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T231" t="n">
@@ -22794,7 +22794,7 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T232" t="n">
@@ -22889,7 +22889,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>03-06-2021 08:30</t>
+          <t>2021-03-06 08:30:00</t>
         </is>
       </c>
       <c r="T233" t="n">
@@ -22984,7 +22984,7 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>01-07-2021 08:30</t>
+          <t>2021-01-07 08:30:00</t>
         </is>
       </c>
       <c r="T234" t="n">
@@ -23079,7 +23079,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T235" t="n">
@@ -23174,7 +23174,7 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T236" t="n">
@@ -23269,7 +23269,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T237" t="n">
@@ -23364,7 +23364,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T238" t="n">
@@ -23459,7 +23459,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T239" t="n">
@@ -23554,7 +23554,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T240" t="n">
@@ -23655,7 +23655,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T241" t="n">
@@ -23754,7 +23754,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T242" t="n">
@@ -23855,7 +23855,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T243" t="n">
@@ -23956,7 +23956,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T244" t="n">
@@ -24055,7 +24055,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T245" t="n">
@@ -24154,7 +24154,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T246" t="n">
@@ -24253,7 +24253,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T247" t="n">
@@ -24354,7 +24354,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T248" t="n">
@@ -24455,7 +24455,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T249" t="n">
@@ -24556,7 +24556,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T250" t="n">
@@ -24655,7 +24655,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T251" t="inlineStr"/>
@@ -24752,7 +24752,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T252" t="n">
@@ -24851,7 +24851,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T253" t="n">
@@ -24952,7 +24952,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T254" t="n">
@@ -25051,7 +25051,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T255" t="n">
@@ -25150,7 +25150,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T256" t="n">
@@ -25251,7 +25251,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T257" t="n">
@@ -25350,7 +25350,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T258" t="n">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T259" t="n">
@@ -25550,7 +25550,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T260" t="n">
@@ -25651,7 +25651,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T261" t="n">
@@ -25746,7 +25746,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T262" t="n">
@@ -25841,7 +25841,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T263" t="n">
@@ -25936,7 +25936,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T264" t="n">
@@ -26031,7 +26031,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T265" t="n">
@@ -26126,7 +26126,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T266" t="n">
@@ -26221,7 +26221,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T267" t="n">
@@ -26316,7 +26316,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T268" t="n">
@@ -26411,7 +26411,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T269" t="n">
@@ -26506,7 +26506,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T270" t="n">
@@ -26601,7 +26601,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T271" t="n">
@@ -26696,7 +26696,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>04-12-2021 08:30</t>
+          <t>2021-04-12 08:30:00</t>
         </is>
       </c>
       <c r="T272" t="n">
@@ -26791,7 +26791,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T273" t="n">
@@ -26890,7 +26890,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T274" t="n">
@@ -26989,7 +26989,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T275" t="n">
@@ -27084,7 +27084,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T276" t="n">
@@ -27179,7 +27179,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T277" t="n">
@@ -27274,7 +27274,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T278" t="n">
@@ -27369,7 +27369,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T279" t="n">
@@ -27464,7 +27464,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>07-06-2021 08:30</t>
+          <t>2021-07-06 08:30:00</t>
         </is>
       </c>
       <c r="T280" t="n">
@@ -27559,7 +27559,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t>01-07-2021 08:30</t>
+          <t>2021-01-07 08:30:00</t>
         </is>
       </c>
       <c r="T281" t="n">
@@ -27654,7 +27654,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T282" t="n">
@@ -27749,7 +27749,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T283" t="n">
@@ -27844,7 +27844,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T284" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T285" t="n">
@@ -28034,7 +28034,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T286" t="inlineStr"/>
@@ -28127,7 +28127,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T287" t="inlineStr"/>
@@ -28220,7 +28220,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T288" t="inlineStr"/>
@@ -28313,7 +28313,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T289" t="inlineStr"/>
@@ -28406,7 +28406,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T290" t="inlineStr"/>
@@ -28499,7 +28499,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T291" t="inlineStr"/>
@@ -28592,7 +28592,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T292" t="inlineStr"/>
@@ -28685,7 +28685,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T293" t="inlineStr"/>
@@ -28778,7 +28778,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T294" t="inlineStr"/>
@@ -28871,7 +28871,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T295" t="inlineStr"/>
@@ -28964,7 +28964,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T296" t="inlineStr"/>
@@ -29057,7 +29057,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T297" t="inlineStr"/>
@@ -29150,7 +29150,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T298" t="inlineStr"/>
@@ -29243,7 +29243,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T299" t="inlineStr"/>
@@ -29336,7 +29336,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T300" t="inlineStr"/>
@@ -29429,7 +29429,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T301" t="n">
@@ -29524,7 +29524,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T302" t="n">
@@ -29619,7 +29619,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T303" t="n">
@@ -29714,7 +29714,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T304" t="n">
@@ -29809,7 +29809,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>01-05-2021 08:30</t>
+          <t>2021-01-05 08:30:00</t>
         </is>
       </c>
       <c r="T305" t="n">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>01-06-2021 08:30</t>
+          <t>2021-01-06 08:30:00</t>
         </is>
       </c>
       <c r="T306" t="n">
@@ -29999,7 +29999,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>01-07-2021 08:30</t>
+          <t>2021-01-07 08:30:00</t>
         </is>
       </c>
       <c r="T307" t="n">
@@ -30094,7 +30094,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>04-08-2021 08:30</t>
+          <t>2021-04-08 08:30:00</t>
         </is>
       </c>
       <c r="T308" t="n">
@@ -30189,7 +30189,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T309" t="n">
@@ -30284,7 +30284,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T310" t="n">
@@ -30379,7 +30379,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T311" t="n">
@@ -30474,7 +30474,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>08-12-2021 08:30</t>
+          <t>2021-08-12 08:30:00</t>
         </is>
       </c>
       <c r="T312" t="n">
@@ -30569,7 +30569,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T313" t="n">
@@ -30664,7 +30664,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T314" t="n">
@@ -30759,7 +30759,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T315" t="n">
@@ -30854,7 +30854,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T316" t="n">
@@ -30949,7 +30949,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T317" t="n">
@@ -31044,7 +31044,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>01-06-2021 08:30</t>
+          <t>2021-01-06 08:30:00</t>
         </is>
       </c>
       <c r="T318" t="n">
@@ -31139,7 +31139,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T319" t="n">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T320" t="n">
@@ -31329,7 +31329,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T321" t="n">
@@ -31424,7 +31424,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T322" t="n">
@@ -31519,7 +31519,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t>08-11-2021 08:30</t>
+          <t>2021-08-11 08:30:00</t>
         </is>
       </c>
       <c r="T323" t="n">
@@ -31614,7 +31614,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>02-12-2021 08:30</t>
+          <t>2021-02-12 08:30:00</t>
         </is>
       </c>
       <c r="T324" t="n">
@@ -31709,7 +31709,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T325" t="n">
@@ -31804,7 +31804,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T326" t="n">
@@ -31899,7 +31899,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T327" t="n">
@@ -31994,7 +31994,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>02-04-2021 08:30</t>
+          <t>2021-02-04 08:30:00</t>
         </is>
       </c>
       <c r="T328" t="n">
@@ -32089,7 +32089,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T329" t="n">
@@ -32184,7 +32184,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>02-06-2021 08:30</t>
+          <t>2021-02-06 08:30:00</t>
         </is>
       </c>
       <c r="T330" t="n">
@@ -32279,7 +32279,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t>07-07-2021 08:30</t>
+          <t>2021-07-07 08:30:00</t>
         </is>
       </c>
       <c r="T331" t="n">
@@ -32374,7 +32374,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t>06-08-2021 08:30</t>
+          <t>2021-06-08 08:30:00</t>
         </is>
       </c>
       <c r="T332" t="n">
@@ -32469,7 +32469,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t>04-09-2021 08:30</t>
+          <t>2021-04-09 08:30:00</t>
         </is>
       </c>
       <c r="T333" t="n">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T334" t="n">
@@ -32659,7 +32659,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T335" t="n">
@@ -32754,7 +32754,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>02-12-2021 08:30</t>
+          <t>2021-02-12 08:30:00</t>
         </is>
       </c>
       <c r="T336" t="n">
@@ -32849,7 +32849,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T337" t="inlineStr"/>
@@ -32942,7 +32942,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T338" t="inlineStr"/>
@@ -33035,7 +33035,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T339" t="inlineStr"/>
@@ -33128,7 +33128,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T340" t="inlineStr"/>
@@ -33221,7 +33221,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T341" t="inlineStr"/>
@@ -33314,7 +33314,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T342" t="inlineStr"/>
@@ -33407,7 +33407,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T343" t="inlineStr"/>
@@ -33500,7 +33500,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T344" t="inlineStr"/>
@@ -33593,7 +33593,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T345" t="inlineStr"/>
@@ -33686,7 +33686,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T346" t="inlineStr"/>
@@ -33779,7 +33779,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T347" t="inlineStr"/>
@@ -33872,7 +33872,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T348" t="inlineStr"/>
@@ -33965,7 +33965,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T349" t="inlineStr"/>
@@ -34058,7 +34058,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T350" t="inlineStr"/>
@@ -34151,7 +34151,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T351" t="inlineStr"/>
@@ -34244,7 +34244,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T352" t="n">
@@ -34339,7 +34339,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T353" t="n">
@@ -34434,7 +34434,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T354" t="n">
@@ -34529,7 +34529,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T355" t="n">
@@ -34624,7 +34624,7 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T356" t="n">
@@ -34719,7 +34719,7 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t>01-06-2021 08:30</t>
+          <t>2021-01-06 08:30:00</t>
         </is>
       </c>
       <c r="T357" t="n">
@@ -34814,7 +34814,7 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t>01-07-2021 08:30</t>
+          <t>2021-01-07 08:30:00</t>
         </is>
       </c>
       <c r="T358" t="n">
@@ -34909,7 +34909,7 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T359" t="n">
@@ -35004,7 +35004,7 @@
       </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T360" t="n">
@@ -35099,7 +35099,7 @@
       </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T361" t="n">
@@ -35194,7 +35194,7 @@
       </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T362" t="n">
@@ -35289,7 +35289,7 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T363" t="n">
@@ -35384,7 +35384,7 @@
       </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T364" t="inlineStr"/>
@@ -35481,7 +35481,7 @@
       </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T365" t="inlineStr"/>
@@ -35578,7 +35578,7 @@
       </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T366" t="inlineStr"/>
@@ -35675,7 +35675,7 @@
       </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T367" t="inlineStr"/>
@@ -35772,7 +35772,7 @@
       </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T368" t="inlineStr"/>
@@ -35869,7 +35869,7 @@
       </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t>02-06-2021 08:30</t>
+          <t>2021-02-06 08:30:00</t>
         </is>
       </c>
       <c r="T369" t="inlineStr"/>
@@ -35966,7 +35966,7 @@
       </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T370" t="inlineStr"/>
@@ -36063,7 +36063,7 @@
       </c>
       <c r="S371" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T371" t="inlineStr"/>
@@ -36160,7 +36160,7 @@
       </c>
       <c r="S372" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T372" t="inlineStr"/>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T373" t="inlineStr"/>
@@ -36354,7 +36354,7 @@
       </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T374" t="inlineStr"/>
@@ -36451,7 +36451,7 @@
       </c>
       <c r="S375" t="inlineStr">
         <is>
-          <t>02-12-2021 08:30</t>
+          <t>2021-02-12 08:30:00</t>
         </is>
       </c>
       <c r="T375" t="inlineStr"/>
@@ -36548,7 +36548,7 @@
       </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T376" t="inlineStr"/>
@@ -36641,7 +36641,7 @@
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T377" t="inlineStr"/>
@@ -36734,7 +36734,7 @@
       </c>
       <c r="S378" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T378" t="inlineStr"/>
@@ -36827,7 +36827,7 @@
       </c>
       <c r="S379" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T379" t="inlineStr"/>
@@ -36920,7 +36920,7 @@
       </c>
       <c r="S380" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T380" t="inlineStr"/>
@@ -37013,7 +37013,7 @@
       </c>
       <c r="S381" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T381" t="inlineStr"/>
@@ -37106,7 +37106,7 @@
       </c>
       <c r="S382" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T382" t="n">
@@ -37201,7 +37201,7 @@
       </c>
       <c r="S383" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T383" t="n">
@@ -37296,7 +37296,7 @@
       </c>
       <c r="S384" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T384" t="n">
@@ -37391,7 +37391,7 @@
       </c>
       <c r="S385" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T385" t="n">
@@ -37486,7 +37486,7 @@
       </c>
       <c r="S386" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T386" t="n">
@@ -37581,7 +37581,7 @@
       </c>
       <c r="S387" t="inlineStr">
         <is>
-          <t>01-06-2021 08:30</t>
+          <t>2021-01-06 08:30:00</t>
         </is>
       </c>
       <c r="T387" t="n">
@@ -37676,7 +37676,7 @@
       </c>
       <c r="S388" t="inlineStr">
         <is>
-          <t>01-07-2021 08:30</t>
+          <t>2021-01-07 08:30:00</t>
         </is>
       </c>
       <c r="T388" t="n">
@@ -37771,7 +37771,7 @@
       </c>
       <c r="S389" t="inlineStr">
         <is>
-          <t>04-08-2021 08:30</t>
+          <t>2021-04-08 08:30:00</t>
         </is>
       </c>
       <c r="T389" t="n">
@@ -37866,7 +37866,7 @@
       </c>
       <c r="S390" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T390" t="n">
@@ -37961,7 +37961,7 @@
       </c>
       <c r="S391" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T391" t="n">
@@ -38056,7 +38056,7 @@
       </c>
       <c r="S392" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T392" t="n">
@@ -38151,7 +38151,7 @@
       </c>
       <c r="S393" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T393" t="n">
@@ -38246,7 +38246,7 @@
       </c>
       <c r="S394" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T394" t="n">
@@ -38345,7 +38345,7 @@
       </c>
       <c r="S395" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T395" t="n">
@@ -38444,7 +38444,7 @@
       </c>
       <c r="S396" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T396" t="n">
@@ -38539,7 +38539,7 @@
       </c>
       <c r="S397" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T397" t="n">
@@ -38634,7 +38634,7 @@
       </c>
       <c r="S398" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T398" t="n">
@@ -38729,7 +38729,7 @@
       </c>
       <c r="S399" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T399" t="n">
@@ -38824,7 +38824,7 @@
       </c>
       <c r="S400" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T400" t="n">
@@ -38919,7 +38919,7 @@
       </c>
       <c r="S401" t="inlineStr">
         <is>
-          <t>01-06-2021 08:30</t>
+          <t>2021-01-06 08:30:00</t>
         </is>
       </c>
       <c r="T401" t="n">
@@ -39014,7 +39014,7 @@
       </c>
       <c r="S402" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T402" t="n">
@@ -39109,7 +39109,7 @@
       </c>
       <c r="S403" t="inlineStr">
         <is>
-          <t>04-08-2021 08:30</t>
+          <t>2021-04-08 08:30:00</t>
         </is>
       </c>
       <c r="T403" t="n">
@@ -39204,7 +39204,7 @@
       </c>
       <c r="S404" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T404" t="n">
@@ -39299,7 +39299,7 @@
       </c>
       <c r="S405" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T405" t="n">
@@ -39394,7 +39394,7 @@
       </c>
       <c r="S406" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T406" t="n">
@@ -39489,7 +39489,7 @@
       </c>
       <c r="S407" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T407" t="n">
@@ -39584,7 +39584,7 @@
       </c>
       <c r="S408" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T408" t="n">
@@ -39679,7 +39679,7 @@
       </c>
       <c r="S409" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T409" t="n">
@@ -39774,7 +39774,7 @@
       </c>
       <c r="S410" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T410" t="n">
@@ -39869,7 +39869,7 @@
       </c>
       <c r="S411" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T411" t="n">
@@ -39964,7 +39964,7 @@
       </c>
       <c r="S412" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T412" t="n">
@@ -40059,7 +40059,7 @@
       </c>
       <c r="S413" t="inlineStr">
         <is>
-          <t>01-06-2021 08:30</t>
+          <t>2021-01-06 08:30:00</t>
         </is>
       </c>
       <c r="T413" t="n">
@@ -40154,7 +40154,7 @@
       </c>
       <c r="S414" t="inlineStr">
         <is>
-          <t>01-07-2021 08:30</t>
+          <t>2021-01-07 08:30:00</t>
         </is>
       </c>
       <c r="T414" t="n">
@@ -40249,7 +40249,7 @@
       </c>
       <c r="S415" t="inlineStr">
         <is>
-          <t>06-08-2021 08:30</t>
+          <t>2021-06-08 08:30:00</t>
         </is>
       </c>
       <c r="T415" t="n">
@@ -40344,7 +40344,7 @@
       </c>
       <c r="S416" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T416" t="n">
@@ -40439,7 +40439,7 @@
       </c>
       <c r="S417" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T417" t="n">
@@ -40534,7 +40534,7 @@
       </c>
       <c r="S418" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T418" t="n">
@@ -40629,7 +40629,7 @@
       </c>
       <c r="S419" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T419" t="n">
@@ -40724,7 +40724,7 @@
       </c>
       <c r="S420" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T420" t="inlineStr"/>
@@ -40817,7 +40817,7 @@
       </c>
       <c r="S421" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T421" t="inlineStr"/>
@@ -40910,7 +40910,7 @@
       </c>
       <c r="S422" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T422" t="inlineStr"/>
@@ -41003,7 +41003,7 @@
       </c>
       <c r="S423" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T423" t="inlineStr"/>
@@ -41096,7 +41096,7 @@
       </c>
       <c r="S424" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T424" t="inlineStr"/>
@@ -41189,7 +41189,7 @@
       </c>
       <c r="S425" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T425" t="inlineStr"/>
@@ -41282,7 +41282,7 @@
       </c>
       <c r="S426" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T426" t="inlineStr"/>
@@ -41375,7 +41375,7 @@
       </c>
       <c r="S427" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T427" t="inlineStr"/>
@@ -41468,7 +41468,7 @@
       </c>
       <c r="S428" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T428" t="inlineStr"/>
@@ -41561,7 +41561,7 @@
       </c>
       <c r="S429" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T429" t="inlineStr"/>
@@ -41654,7 +41654,7 @@
       </c>
       <c r="S430" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T430" t="inlineStr"/>
@@ -41747,7 +41747,7 @@
       </c>
       <c r="S431" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T431" t="inlineStr"/>
@@ -41840,7 +41840,7 @@
       </c>
       <c r="S432" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T432" t="inlineStr"/>
@@ -41933,7 +41933,7 @@
       </c>
       <c r="S433" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T433" t="inlineStr"/>
@@ -42026,7 +42026,7 @@
       </c>
       <c r="S434" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T434" t="inlineStr"/>
@@ -42119,7 +42119,7 @@
       </c>
       <c r="S435" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T435" t="inlineStr"/>
@@ -42212,7 +42212,7 @@
       </c>
       <c r="S436" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T436" t="n">
@@ -42307,7 +42307,7 @@
       </c>
       <c r="S437" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T437" t="n">
@@ -42402,7 +42402,7 @@
       </c>
       <c r="S438" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T438" t="inlineStr"/>
@@ -42495,7 +42495,7 @@
       </c>
       <c r="S439" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T439" t="n">
@@ -42590,7 +42590,7 @@
       </c>
       <c r="S440" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T440" t="n">
@@ -42685,7 +42685,7 @@
       </c>
       <c r="S441" t="inlineStr">
         <is>
-          <t>01-06-2021 08:30</t>
+          <t>2021-01-06 08:30:00</t>
         </is>
       </c>
       <c r="T441" t="n">
@@ -42780,7 +42780,7 @@
       </c>
       <c r="S442" t="inlineStr">
         <is>
-          <t>01-07-2021 08:30</t>
+          <t>2021-01-07 08:30:00</t>
         </is>
       </c>
       <c r="T442" t="n">
@@ -42875,7 +42875,7 @@
       </c>
       <c r="S443" t="inlineStr">
         <is>
-          <t>07-08-2021 08:30</t>
+          <t>2021-07-08 08:30:00</t>
         </is>
       </c>
       <c r="T443" t="n">
@@ -42970,7 +42970,7 @@
       </c>
       <c r="S444" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T444" t="n">
@@ -43065,7 +43065,7 @@
       </c>
       <c r="S445" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T445" t="n">
@@ -43160,7 +43160,7 @@
       </c>
       <c r="S446" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T446" t="n">
@@ -43255,7 +43255,7 @@
       </c>
       <c r="S447" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T447" t="n">
@@ -43350,7 +43350,7 @@
       </c>
       <c r="S448" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T448" t="n">
@@ -43445,7 +43445,7 @@
       </c>
       <c r="S449" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T449" t="n">
@@ -43540,7 +43540,7 @@
       </c>
       <c r="S450" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T450" t="n">
@@ -43635,7 +43635,7 @@
       </c>
       <c r="S451" t="inlineStr">
         <is>
-          <t>01-06-2021 08:30</t>
+          <t>2021-01-06 08:30:00</t>
         </is>
       </c>
       <c r="T451" t="n">
@@ -43730,7 +43730,7 @@
       </c>
       <c r="S452" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T452" t="n">
@@ -43825,7 +43825,7 @@
       </c>
       <c r="S453" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T453" t="n">
@@ -43920,7 +43920,7 @@
       </c>
       <c r="S454" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T454" t="n">
@@ -44015,7 +44015,7 @@
       </c>
       <c r="S455" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T455" t="n">
@@ -44110,7 +44110,7 @@
       </c>
       <c r="S456" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T456" t="n">
@@ -44205,7 +44205,7 @@
       </c>
       <c r="S457" t="inlineStr">
         <is>
-          <t>02-12-2021 08:30</t>
+          <t>2021-02-12 08:30:00</t>
         </is>
       </c>
       <c r="T457" t="n">
@@ -44300,7 +44300,7 @@
       </c>
       <c r="S458" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T458" t="n">
@@ -44395,7 +44395,7 @@
       </c>
       <c r="S459" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T459" t="n">
@@ -44490,7 +44490,7 @@
       </c>
       <c r="S460" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T460" t="n">
@@ -44585,7 +44585,7 @@
       </c>
       <c r="S461" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T461" t="n">
@@ -44680,7 +44680,7 @@
       </c>
       <c r="S462" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T462" t="n">
@@ -44775,7 +44775,7 @@
       </c>
       <c r="S463" t="inlineStr">
         <is>
-          <t>02-06-2021 08:30</t>
+          <t>2021-02-06 08:30:00</t>
         </is>
       </c>
       <c r="T463" t="n">
@@ -44870,7 +44870,7 @@
       </c>
       <c r="S464" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T464" t="n">
@@ -44965,7 +44965,7 @@
       </c>
       <c r="S465" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T465" t="n">
@@ -45060,7 +45060,7 @@
       </c>
       <c r="S466" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T466" t="n">
@@ -45155,7 +45155,7 @@
       </c>
       <c r="S467" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T467" t="n">
@@ -45250,7 +45250,7 @@
       </c>
       <c r="S468" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T468" t="n">
@@ -45345,7 +45345,7 @@
       </c>
       <c r="S469" t="inlineStr">
         <is>
-          <t>02-12-2021 08:30</t>
+          <t>2021-02-12 08:30:00</t>
         </is>
       </c>
       <c r="T469" t="n">
@@ -45440,7 +45440,7 @@
       </c>
       <c r="S470" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T470" t="n">
@@ -45539,7 +45539,7 @@
       </c>
       <c r="S471" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T471" t="n">
@@ -45638,7 +45638,7 @@
       </c>
       <c r="S472" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T472" t="n">
@@ -45737,7 +45737,7 @@
       </c>
       <c r="S473" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T473" t="n">
@@ -45836,7 +45836,7 @@
       </c>
       <c r="S474" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T474" t="inlineStr"/>
@@ -45929,7 +45929,7 @@
       </c>
       <c r="S475" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T475" t="inlineStr"/>
@@ -46022,7 +46022,7 @@
       </c>
       <c r="S476" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T476" t="inlineStr"/>
@@ -46115,7 +46115,7 @@
       </c>
       <c r="S477" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T477" t="inlineStr"/>
@@ -46208,7 +46208,7 @@
       </c>
       <c r="S478" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T478" t="inlineStr"/>
@@ -46301,7 +46301,7 @@
       </c>
       <c r="S479" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T479" t="inlineStr"/>
@@ -46394,7 +46394,7 @@
       </c>
       <c r="S480" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T480" t="inlineStr"/>
@@ -46487,7 +46487,7 @@
       </c>
       <c r="S481" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T481" t="inlineStr"/>
@@ -46580,7 +46580,7 @@
       </c>
       <c r="S482" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T482" t="inlineStr"/>
@@ -46673,7 +46673,7 @@
       </c>
       <c r="S483" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T483" t="inlineStr"/>
@@ -46766,7 +46766,7 @@
       </c>
       <c r="S484" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T484" t="inlineStr"/>
@@ -46859,7 +46859,7 @@
       </c>
       <c r="S485" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T485" t="inlineStr"/>
@@ -46952,7 +46952,7 @@
       </c>
       <c r="S486" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T486" t="inlineStr"/>
@@ -47045,7 +47045,7 @@
       </c>
       <c r="S487" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T487" t="inlineStr"/>
@@ -47138,7 +47138,7 @@
       </c>
       <c r="S488" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T488" t="inlineStr"/>
@@ -47231,7 +47231,7 @@
       </c>
       <c r="S489" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T489" t="inlineStr"/>
@@ -47324,7 +47324,7 @@
       </c>
       <c r="S490" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T490" t="inlineStr"/>
@@ -47417,7 +47417,7 @@
       </c>
       <c r="S491" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T491" t="inlineStr"/>
@@ -47510,7 +47510,7 @@
       </c>
       <c r="S492" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T492" t="inlineStr"/>
@@ -47603,7 +47603,7 @@
       </c>
       <c r="S493" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T493" t="inlineStr"/>
@@ -47696,7 +47696,7 @@
       </c>
       <c r="S494" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T494" t="inlineStr"/>
@@ -47789,7 +47789,7 @@
       </c>
       <c r="S495" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T495" t="inlineStr"/>
@@ -47882,7 +47882,7 @@
       </c>
       <c r="S496" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T496" t="inlineStr"/>
@@ -47975,7 +47975,7 @@
       </c>
       <c r="S497" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T497" t="inlineStr"/>
@@ -48068,7 +48068,7 @@
       </c>
       <c r="S498" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T498" t="inlineStr"/>
@@ -48161,7 +48161,7 @@
       </c>
       <c r="S499" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T499" t="inlineStr"/>
@@ -48254,7 +48254,7 @@
       </c>
       <c r="S500" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T500" t="inlineStr"/>
@@ -48347,7 +48347,7 @@
       </c>
       <c r="S501" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T501" t="inlineStr"/>
@@ -48440,7 +48440,7 @@
       </c>
       <c r="S502" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T502" t="inlineStr"/>
@@ -48533,7 +48533,7 @@
       </c>
       <c r="S503" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T503" t="inlineStr"/>
@@ -48626,7 +48626,7 @@
       </c>
       <c r="S504" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T504" t="inlineStr"/>
@@ -48719,7 +48719,7 @@
       </c>
       <c r="S505" t="inlineStr">
         <is>
-          <t>01-07-2021 08:30</t>
+          <t>2021-01-07 08:30:00</t>
         </is>
       </c>
       <c r="T505" t="n">
@@ -48814,7 +48814,7 @@
       </c>
       <c r="S506" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T506" t="n">
@@ -48913,7 +48913,7 @@
       </c>
       <c r="S507" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T507" t="n">
@@ -49012,7 +49012,7 @@
       </c>
       <c r="S508" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T508" t="inlineStr"/>
@@ -49105,7 +49105,7 @@
       </c>
       <c r="S509" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T509" t="inlineStr"/>
@@ -49198,7 +49198,7 @@
       </c>
       <c r="S510" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T510" t="inlineStr"/>
@@ -49291,7 +49291,7 @@
       </c>
       <c r="S511" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T511" t="n">
@@ -49386,7 +49386,7 @@
       </c>
       <c r="S512" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T512" t="n">
@@ -49481,7 +49481,7 @@
       </c>
       <c r="S513" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T513" t="n">
@@ -49576,7 +49576,7 @@
       </c>
       <c r="S514" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T514" t="n">
@@ -49671,7 +49671,7 @@
       </c>
       <c r="S515" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T515" t="n">
@@ -49766,7 +49766,7 @@
       </c>
       <c r="S516" t="inlineStr">
         <is>
-          <t>02-06-2021 08:30</t>
+          <t>2021-02-06 08:30:00</t>
         </is>
       </c>
       <c r="T516" t="n">
@@ -49861,7 +49861,7 @@
       </c>
       <c r="S517" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T517" t="n">
@@ -49956,7 +49956,7 @@
       </c>
       <c r="S518" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T518" t="n">
@@ -50051,7 +50051,7 @@
       </c>
       <c r="S519" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T519" t="n">
@@ -50146,7 +50146,7 @@
       </c>
       <c r="S520" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T520" t="n">
@@ -50241,7 +50241,7 @@
       </c>
       <c r="S521" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T521" t="n">
@@ -50336,7 +50336,7 @@
       </c>
       <c r="S522" t="inlineStr">
         <is>
-          <t>04-12-2021 08:30</t>
+          <t>2021-04-12 08:30:00</t>
         </is>
       </c>
       <c r="T522" t="n">
@@ -50431,7 +50431,7 @@
       </c>
       <c r="S523" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T523" t="inlineStr"/>
@@ -50524,7 +50524,7 @@
       </c>
       <c r="S524" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T524" t="inlineStr"/>
@@ -50617,7 +50617,7 @@
       </c>
       <c r="S525" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T525" t="inlineStr"/>
@@ -50710,7 +50710,7 @@
       </c>
       <c r="S526" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T526" t="inlineStr"/>
@@ -50803,7 +50803,7 @@
       </c>
       <c r="S527" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T527" t="inlineStr"/>
@@ -50896,7 +50896,7 @@
       </c>
       <c r="S528" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T528" t="inlineStr"/>
@@ -50989,7 +50989,7 @@
       </c>
       <c r="S529" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T529" t="inlineStr"/>
@@ -51082,7 +51082,7 @@
       </c>
       <c r="S530" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T530" t="inlineStr"/>
@@ -51175,7 +51175,7 @@
       </c>
       <c r="S531" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T531" t="inlineStr"/>
@@ -51268,7 +51268,7 @@
       </c>
       <c r="S532" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T532" t="inlineStr"/>
@@ -51361,7 +51361,7 @@
       </c>
       <c r="S533" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T533" t="inlineStr"/>
@@ -51454,7 +51454,7 @@
       </c>
       <c r="S534" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T534" t="inlineStr"/>
@@ -51547,7 +51547,7 @@
       </c>
       <c r="S535" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T535" t="inlineStr"/>
@@ -51640,7 +51640,7 @@
       </c>
       <c r="S536" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T536" t="inlineStr"/>
@@ -51733,7 +51733,7 @@
       </c>
       <c r="S537" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T537" t="inlineStr"/>
@@ -51826,7 +51826,7 @@
       </c>
       <c r="S538" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T538" t="inlineStr"/>
@@ -51919,7 +51919,7 @@
       </c>
       <c r="S539" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T539" t="n">
@@ -52014,7 +52014,7 @@
       </c>
       <c r="S540" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T540" t="n">
@@ -52109,7 +52109,7 @@
       </c>
       <c r="S541" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T541" t="n">
@@ -52204,7 +52204,7 @@
       </c>
       <c r="S542" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T542" t="n">
@@ -52299,7 +52299,7 @@
       </c>
       <c r="S543" t="inlineStr">
         <is>
-          <t>01-06-2021 08:30</t>
+          <t>2021-01-06 08:30:00</t>
         </is>
       </c>
       <c r="T543" t="n">
@@ -52394,7 +52394,7 @@
       </c>
       <c r="S544" t="inlineStr">
         <is>
-          <t>01-07-2021 08:30</t>
+          <t>2021-01-07 08:30:00</t>
         </is>
       </c>
       <c r="T544" t="n">
@@ -52489,7 +52489,7 @@
       </c>
       <c r="S545" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T545" t="n">
@@ -52584,7 +52584,7 @@
       </c>
       <c r="S546" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T546" t="n">
@@ -52679,7 +52679,7 @@
       </c>
       <c r="S547" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T547" t="n">
@@ -52774,7 +52774,7 @@
       </c>
       <c r="S548" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T548" t="n">
@@ -52869,7 +52869,7 @@
       </c>
       <c r="S549" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T549" t="n">
@@ -52964,7 +52964,7 @@
       </c>
       <c r="S550" t="inlineStr">
         <is>
-          <t>03-01-2021 08:30</t>
+          <t>2021-03-01 08:30:00</t>
         </is>
       </c>
       <c r="T550" t="inlineStr"/>
@@ -53057,7 +53057,7 @@
       </c>
       <c r="S551" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T551" t="inlineStr"/>
@@ -53150,7 +53150,7 @@
       </c>
       <c r="S552" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T552" t="inlineStr"/>
@@ -53243,7 +53243,7 @@
       </c>
       <c r="S553" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T553" t="inlineStr"/>
@@ -53336,7 +53336,7 @@
       </c>
       <c r="S554" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T554" t="inlineStr"/>
@@ -53429,7 +53429,7 @@
       </c>
       <c r="S555" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T555" t="inlineStr"/>
@@ -53522,7 +53522,7 @@
       </c>
       <c r="S556" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T556" t="n">
@@ -53617,7 +53617,7 @@
       </c>
       <c r="S557" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T557" t="n">
@@ -53712,7 +53712,7 @@
       </c>
       <c r="S558" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T558" t="n">
@@ -53807,7 +53807,7 @@
       </c>
       <c r="S559" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T559" t="n">
@@ -53902,7 +53902,7 @@
       </c>
       <c r="S560" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T560" t="n">
@@ -53997,7 +53997,7 @@
       </c>
       <c r="S561" t="inlineStr">
         <is>
-          <t>01-06-2021 08:30</t>
+          <t>2021-01-06 08:30:00</t>
         </is>
       </c>
       <c r="T561" t="n">
@@ -54092,7 +54092,7 @@
       </c>
       <c r="S562" t="inlineStr">
         <is>
-          <t>01-07-2021 08:30</t>
+          <t>2021-01-07 08:30:00</t>
         </is>
       </c>
       <c r="T562" t="n">
@@ -54187,7 +54187,7 @@
       </c>
       <c r="S563" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T563" t="n">
@@ -54282,7 +54282,7 @@
       </c>
       <c r="S564" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T564" t="n">
@@ -54377,7 +54377,7 @@
       </c>
       <c r="S565" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T565" t="n">
@@ -54472,7 +54472,7 @@
       </c>
       <c r="S566" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T566" t="n">
@@ -54567,7 +54567,7 @@
       </c>
       <c r="S567" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T567" t="n">
@@ -54662,7 +54662,7 @@
       </c>
       <c r="S568" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T568" t="inlineStr"/>
@@ -54755,7 +54755,7 @@
       </c>
       <c r="S569" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T569" t="inlineStr"/>
@@ -54848,7 +54848,7 @@
       </c>
       <c r="S570" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T570" t="inlineStr"/>
@@ -54941,7 +54941,7 @@
       </c>
       <c r="S571" t="inlineStr">
         <is>
-          <t>02-04-2021 08:30</t>
+          <t>2021-02-04 08:30:00</t>
         </is>
       </c>
       <c r="T571" t="n">
@@ -55042,7 +55042,7 @@
       </c>
       <c r="S572" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T572" t="n">
@@ -55143,7 +55143,7 @@
       </c>
       <c r="S573" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T573" t="inlineStr"/>
@@ -55240,7 +55240,7 @@
       </c>
       <c r="S574" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T574" t="inlineStr"/>
@@ -55337,7 +55337,7 @@
       </c>
       <c r="S575" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T575" t="inlineStr"/>
@@ -55434,7 +55434,7 @@
       </c>
       <c r="S576" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T576" t="inlineStr"/>
@@ -55531,7 +55531,7 @@
       </c>
       <c r="S577" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T577" t="inlineStr"/>
@@ -55628,7 +55628,7 @@
       </c>
       <c r="S578" t="inlineStr">
         <is>
-          <t>01-06-2021 08:30</t>
+          <t>2021-01-06 08:30:00</t>
         </is>
       </c>
       <c r="T578" t="inlineStr"/>
@@ -55725,7 +55725,7 @@
       </c>
       <c r="S579" t="inlineStr">
         <is>
-          <t>01-07-2021 08:30</t>
+          <t>2021-01-07 08:30:00</t>
         </is>
       </c>
       <c r="T579" t="inlineStr"/>
@@ -55822,7 +55822,7 @@
       </c>
       <c r="S580" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T580" t="inlineStr"/>
@@ -55919,7 +55919,7 @@
       </c>
       <c r="S581" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T581" t="inlineStr"/>
@@ -56016,7 +56016,7 @@
       </c>
       <c r="S582" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T582" t="inlineStr"/>
@@ -56113,7 +56113,7 @@
       </c>
       <c r="S583" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T583" t="inlineStr"/>
@@ -56210,7 +56210,7 @@
       </c>
       <c r="S584" t="inlineStr">
         <is>
-          <t>10-12-2021 08:30</t>
+          <t>2021-10-12 08:30:00</t>
         </is>
       </c>
       <c r="T584" t="inlineStr"/>
@@ -56307,7 +56307,7 @@
       </c>
       <c r="S585" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T585" t="n">
@@ -56406,7 +56406,7 @@
       </c>
       <c r="S586" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T586" t="n">
@@ -56505,7 +56505,7 @@
       </c>
       <c r="S587" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T587" t="inlineStr"/>
@@ -56598,7 +56598,7 @@
       </c>
       <c r="S588" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T588" t="inlineStr"/>
@@ -56691,7 +56691,7 @@
       </c>
       <c r="S589" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T589" t="inlineStr"/>
@@ -56784,7 +56784,7 @@
       </c>
       <c r="S590" t="inlineStr">
         <is>
-          <t>02-06-2021 08:30</t>
+          <t>2021-02-06 08:30:00</t>
         </is>
       </c>
       <c r="T590" t="n">
@@ -56879,7 +56879,7 @@
       </c>
       <c r="S591" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T591" t="n">
@@ -56974,7 +56974,7 @@
       </c>
       <c r="S592" t="inlineStr">
         <is>
-          <t>04-08-2021 08:30</t>
+          <t>2021-04-08 08:30:00</t>
         </is>
       </c>
       <c r="T592" t="n">
@@ -57069,7 +57069,7 @@
       </c>
       <c r="S593" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T593" t="n">
@@ -57164,7 +57164,7 @@
       </c>
       <c r="S594" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T594" t="n">
@@ -57259,7 +57259,7 @@
       </c>
       <c r="S595" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T595" t="n">
@@ -57354,7 +57354,7 @@
       </c>
       <c r="S596" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T596" t="n">
@@ -57453,7 +57453,7 @@
       </c>
       <c r="S597" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T597" t="n">
@@ -57552,7 +57552,7 @@
       </c>
       <c r="S598" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T598" t="inlineStr"/>
@@ -57645,7 +57645,7 @@
       </c>
       <c r="S599" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T599" t="inlineStr"/>
@@ -57738,7 +57738,7 @@
       </c>
       <c r="S600" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T600" t="inlineStr"/>
@@ -57831,7 +57831,7 @@
       </c>
       <c r="S601" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T601" t="inlineStr"/>
@@ -57924,7 +57924,7 @@
       </c>
       <c r="S602" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T602" t="inlineStr"/>
@@ -58017,7 +58017,7 @@
       </c>
       <c r="S603" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T603" t="inlineStr"/>
@@ -58110,7 +58110,7 @@
       </c>
       <c r="S604" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T604" t="n">
@@ -58209,7 +58209,7 @@
       </c>
       <c r="S605" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T605" t="n">
@@ -58308,7 +58308,7 @@
       </c>
       <c r="S606" t="inlineStr">
         <is>
-          <t>04-04-2021 08:30</t>
+          <t>2021-04-04 08:30:00</t>
         </is>
       </c>
       <c r="T606" t="n">
@@ -58407,7 +58407,7 @@
       </c>
       <c r="S607" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T607" t="n">
@@ -58506,7 +58506,7 @@
       </c>
       <c r="S608" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T608" t="n">
@@ -58605,7 +58605,7 @@
       </c>
       <c r="S609" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T609" t="n">
@@ -58704,7 +58704,7 @@
       </c>
       <c r="S610" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T610" t="n">
@@ -58805,7 +58805,7 @@
       </c>
       <c r="S611" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T611" t="n">
@@ -58906,7 +58906,7 @@
       </c>
       <c r="S612" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T612" t="n">
@@ -59005,7 +59005,7 @@
       </c>
       <c r="S613" t="inlineStr">
         <is>
-          <t>28-09-2021 08:30</t>
+          <t>2021-09-28 08:30:00</t>
         </is>
       </c>
       <c r="T613" t="n">
@@ -59104,7 +59104,7 @@
       </c>
       <c r="S614" t="inlineStr">
         <is>
-          <t>28-09-2021 08:30</t>
+          <t>2021-09-28 08:30:00</t>
         </is>
       </c>
       <c r="T614" t="n">
@@ -59203,7 +59203,7 @@
       </c>
       <c r="S615" t="inlineStr">
         <is>
-          <t>28-09-2021 08:30</t>
+          <t>2021-09-28 08:30:00</t>
         </is>
       </c>
       <c r="T615" t="n">
@@ -59302,7 +59302,7 @@
       </c>
       <c r="S616" t="inlineStr">
         <is>
-          <t>28-09-2021 08:30</t>
+          <t>2021-09-28 08:30:00</t>
         </is>
       </c>
       <c r="T616" t="n">
@@ -59403,7 +59403,7 @@
       </c>
       <c r="S617" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T617" t="n">
@@ -59502,7 +59502,7 @@
       </c>
       <c r="S618" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T618" t="n">
@@ -59601,7 +59601,7 @@
       </c>
       <c r="S619" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T619" t="n">
@@ -59700,7 +59700,7 @@
       </c>
       <c r="S620" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T620" t="n">
@@ -59799,7 +59799,7 @@
       </c>
       <c r="S621" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T621" t="n">
@@ -59898,7 +59898,7 @@
       </c>
       <c r="S622" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T622" t="n">
